--- a/outputs/유효생산량_결과_2026-05.xlsx
+++ b/outputs/유효생산량_결과_2026-05.xlsx
@@ -953,7 +953,7 @@
         <v>46159</v>
       </c>
       <c r="B18" t="n">
-        <v>1006631</v>
+        <v>1006331</v>
       </c>
       <c r="C18" t="n">
         <v>10805364</v>
@@ -965,16 +965,16 @@
         <v>162653</v>
       </c>
       <c r="F18" t="n">
-        <v>433990</v>
+        <v>433690</v>
       </c>
       <c r="G18" t="n">
-        <v>40.72872780591895</v>
+        <v>40.74086955484826</v>
       </c>
       <c r="H18" t="n">
-        <v>16.15815527238879</v>
+        <v>16.16297222285709</v>
       </c>
       <c r="I18" t="n">
-        <v>43.11311692169226</v>
+        <v>43.09615822229465</v>
       </c>
     </row>
     <row r="19">
@@ -1243,7 +1243,7 @@
         <v>46169</v>
       </c>
       <c r="B28" t="n">
-        <v>1036808</v>
+        <v>1036708</v>
       </c>
       <c r="C28" t="n">
         <v>11423763</v>
@@ -1252,19 +1252,19 @@
         <v>541221</v>
       </c>
       <c r="E28" t="n">
-        <v>150007</v>
+        <v>149907</v>
       </c>
       <c r="F28" t="n">
         <v>345580</v>
       </c>
       <c r="G28" t="n">
-        <v>52.20069675388307</v>
+        <v>52.20573199010715</v>
       </c>
       <c r="H28" t="n">
-        <v>14.46815610990656</v>
+        <v>14.45990577867635</v>
       </c>
       <c r="I28" t="n">
-        <v>33.33114713621037</v>
+        <v>33.3343622312165</v>
       </c>
     </row>
   </sheetData>
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>55540</v>
+        <v>55240</v>
       </c>
       <c r="E381" t="n">
         <v>25654</v>
@@ -16146,16 +16146,16 @@
         <v>362</v>
       </c>
       <c r="H381" t="n">
-        <v>53070</v>
+        <v>52770</v>
       </c>
       <c r="I381" t="n">
-        <v>3.795462729564278</v>
+        <v>3.816075307748009</v>
       </c>
       <c r="J381" t="n">
-        <v>0.6517824990997479</v>
+        <v>0.6553222302679218</v>
       </c>
       <c r="K381" t="n">
-        <v>95.55275477133598</v>
+        <v>95.52860246198406</v>
       </c>
     </row>
     <row r="382">
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="D611" t="n">
-        <v>23160</v>
+        <v>23060</v>
       </c>
       <c r="E611" t="n">
         <v>46126</v>
@@ -25113,19 +25113,19 @@
         <v>318</v>
       </c>
       <c r="G611" t="n">
-        <v>7302</v>
+        <v>7202</v>
       </c>
       <c r="H611" t="n">
         <v>15540</v>
       </c>
       <c r="I611" t="n">
-        <v>1.373056994818653</v>
+        <v>1.379011274934952</v>
       </c>
       <c r="J611" t="n">
-        <v>31.52849740932642</v>
+        <v>31.23156981786643</v>
       </c>
       <c r="K611" t="n">
-        <v>67.09844559585493</v>
+        <v>67.38941890719862</v>
       </c>
     </row>
     <row r="612">
